--- a/PARADISE_WP1_afvinklijst.xlsx
+++ b/PARADISE_WP1_afvinklijst.xlsx
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Pedar als klinisch toestel met trublu-kalibratie; F-Scan GO alleen studieteam; acht regio's; norm &lt; 200 kPa óf ≥ 25% reductie; behaalde reductie als fidelity-maat</t>
+          <t>Pedar als klinisch toestel met trublu-kalibratie; F-Scan GO alleen studieteam; acht regio's; alles in-shoe, zónder én mét de zool gemeten; norm &lt; 200 kPa mét de zool óf ≥ 25% lager dan zonder, in dezelfde sessie; behaalde reductie als fidelity-maat</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
@@ -4277,8 +4277,8 @@
   <mergeCells count="11">
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A60:I60"/>
     <mergeCell ref="A1:I1"/>
@@ -4992,6 +4992,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="25" t="inlineStr">
         <is>
@@ -5008,7 +5009,7 @@
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>Alles in-shoe. De baseline meet zónder de CMFO, alle latere metingen mét. Tabel 4 van het manuscript had het dus goed</t>
+          <t>Alles in-shoe, twee condities: zónder en mét de CMFO. De 25%-reductie is het verschil tussen die twee, in dezelfde sessie gemeten. Tabel 4 van het manuscript had het goed</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -5074,7 +5075,7 @@
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>Vraagt nu drie condities; de blootsvoetse vervalt</t>
+          <t>De blootsvoetse conditie vervalt; de twee overblijvende condities worden op elk meetmoment allebei gemeten</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -5140,7 +5141,7 @@
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>Wordt de meting zónder zool herhaald als een deelnemer later ander schoeisel krijgt? Anders slaat de referentie op een schoen die hij niet meer draagt</t>
+          <t>Beantwoord: de meting zónder zool hoort bij elk meetmoment, dus er is geen oude referentie die kan verouderen</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -5155,12 +5156,12 @@
       </c>
       <c r="F32" s="23" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Vervalt</t>
         </is>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
-          <t>Raakt de formule voor de 25%-reductie</t>
+          <t>Opgelost door de beslissing</t>
         </is>
       </c>
     </row>

--- a/PARADISE_WP1_afvinklijst.xlsx
+++ b/PARADISE_WP1_afvinklijst.xlsx
@@ -211,7 +211,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -260,6 +260,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -971,27 +974,27 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTA('Openstaande punten'!$F$5:$F$32)</f>
+        <f>COUNTA('Openstaande punten'!$F$5:$F$37)</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>COUNTIF('Openstaande punten'!$F$5:$F$32,"Te doen")</f>
+        <f>COUNTIF('Openstaande punten'!$F$5:$F$37,"Te doen")</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>COUNTIF('Openstaande punten'!$F$5:$F$32,"Bezig")</f>
+        <f>COUNTIF('Openstaande punten'!$F$5:$F$37,"Bezig")</f>
         <v/>
       </c>
       <c r="E8" s="5">
-        <f>COUNTIF('Openstaande punten'!$F$5:$F$32,"Klaar")</f>
+        <f>COUNTIF('Openstaande punten'!$F$5:$F$37,"Klaar")</f>
         <v/>
       </c>
       <c r="F8" s="5">
-        <f>COUNTIF('Openstaande punten'!$F$5:$F$32,"Geblokkeerd")</f>
+        <f>COUNTIF('Openstaande punten'!$F$5:$F$37,"Geblokkeerd")</f>
         <v/>
       </c>
       <c r="G8" s="5">
-        <f>COUNTIF('Openstaande punten'!$F$5:$F$32,"Vervalt")</f>
+        <f>COUNTIF('Openstaande punten'!$F$5:$F$37,"Vervalt")</f>
         <v/>
       </c>
       <c r="H8" s="5">
@@ -4276,8 +4279,8 @@
   <autoFilter ref="A4:I79"/>
   <mergeCells count="11">
     <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A73:I73"/>
-    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A60:I60"/>
@@ -4320,7 +4323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="14" min="1" max="1"/>
@@ -5162,6 +5165,171 @@
       <c r="G32" s="23" t="inlineStr">
         <is>
           <t>Opgelost door de beslissing</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="26" t="inlineStr"/>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Palet op 200 kPa zetten en verdelen</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>Hoogste niveau op 200 kPa, het niveau van 220 eruit. Bewaren met 'Save custom set' en op alle zes de laptops laden, anders zijn de schermafbeeldingen onderling niet vergelijkbaar</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>novel studio, zes centra</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>Vervangt de segmentatie tot die er is</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="26" t="inlineStr"/>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>eCRF-Excel: veld voor de schermafbeelding</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>Per deelnemer, meetmoment en conditie een plek om het MPP-beeld in te plakken, plus velden voor de drie hoogste waarden met hun plaats</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>eCRF 09, eCRF 24</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>Volgt uit de beslissing van 11 sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="26" t="inlineStr"/>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Set Range toetsen in de droogloop</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>Nagaan of MPP en MVP herberekend worden over de selectie, of dat alleen de grafiek inzoomt. Eén opname twee keer aflezen, volledig en met selectie</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>droogloop november</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>Middel</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>Openstaand punt 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="26" t="inlineStr"/>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>MVP-weergave kiezen voor de secundaire analyses</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>MVP O telt alle frames mee, MVP LF alleen geladen frames, MVP LC ook zonder nulsensoren. Voor de norm maakt het niet uit: die gaat op MPP</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>SAP, eCRF 24</t>
+        </is>
+      </c>
+      <c r="E36" s="23" t="inlineStr">
+        <is>
+          <t>Middel</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>Openstaand punt 28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="26" t="inlineStr"/>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>Schoenmaat 46 en groter</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>Wordt gemeten met YW (44/45); de zool vangt het maatverschil op. Geen ZW bijbestellen, schoenmaat is geen uitsluitingsgrond</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>SOP 09b</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>Klaar</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t>Beslist 11 sep</t>
         </is>
       </c>
     </row>

--- a/PARADISE_WP1_afvinklijst.xlsx
+++ b/PARADISE_WP1_afvinklijst.xlsx
@@ -4279,9 +4279,9 @@
   <autoFilter ref="A4:I79"/>
   <mergeCells count="11">
     <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A73:I73"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A60:I60"/>
     <mergeCell ref="A1:I1"/>
@@ -4323,7 +4323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="14" min="1" max="1"/>
@@ -4646,7 +4646,7 @@
       <c r="G13" s="10" t="n"/>
     </row>
     <row r="14" ht="25.5" customHeight="1" s="14">
-      <c r="A14" s="24" t="n">
+      <c r="A14" s="26" t="n">
         <v>8</v>
       </c>
       <c r="B14" s="23" t="inlineStr">
@@ -4995,7 +4995,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="25" t="inlineStr">
         <is>
@@ -5004,7 +5003,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr"/>
+      <c r="A28" s="26" t="inlineStr"/>
       <c r="B28" s="23" t="inlineStr">
         <is>
           <t>Blootsvoets of in-shoe — beslist</t>
@@ -5037,7 +5036,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr"/>
+      <c r="A29" s="26" t="inlineStr"/>
       <c r="B29" s="23" t="inlineStr">
         <is>
           <t>eCRF 09 bijwerken</t>
@@ -5070,7 +5069,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr"/>
+      <c r="A30" s="26" t="inlineStr"/>
       <c r="B30" s="23" t="inlineStr">
         <is>
           <t>eCRF 24 bijwerken</t>
@@ -5103,7 +5102,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr"/>
+      <c r="A31" s="26" t="inlineStr"/>
       <c r="B31" s="23" t="inlineStr">
         <is>
           <t>SOP-2 en opleidingsmodule 3 bijwerken</t>
@@ -5136,7 +5135,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="24" t="inlineStr"/>
+      <c r="A32" s="26" t="inlineStr"/>
       <c r="B32" s="23" t="inlineStr">
         <is>
           <t>Referentie bij nieuw schoeisel beslissen</t>
@@ -5300,7 +5299,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" s="14">
       <c r="A37" s="26" t="inlineStr"/>
       <c r="B37" s="23" t="inlineStr">
         <is>
@@ -5330,6 +5329,204 @@
       <c r="G37" s="23" t="inlineStr">
         <is>
           <t>Beslist 11 sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" s="14">
+      <c r="A38" s="26" t="n"/>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>Novel database aanmaken</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>De suite novel scientific 29.3.25 staat geïnstalleerd op de onderzoekslaptop (C:\novel, met SQL Server Express 2019), maar er is nog geen database: geen deelnemers, geen pedar-bestanden. Beslissen of er één centrale database komt of één per centrum.</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>novel database</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>Openstaand punt 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" s="14">
+      <c r="A39" s="26" t="n"/>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>Masker met de acht regio's tekenen</t>
+        </is>
+      </c>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>Met 'creation of any and percent masks' de acht protocolregio's als percent mask op een referentiezool zetten. Daarna rekent 'multimask evaluation' per meting en 'groupmask evaluation' over alle metingen de piekdruk per regio uit. Dit vervangt het aflezen op het palet als analysemethode.</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>novel database</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr">
+        <is>
+          <t>Lost punt 26 op</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" s="14">
+      <c r="A40" s="26" t="n"/>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>Identificatie in het veld Persons vastleggen</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>De database vraagt uit zichzelf naam en geboortedatum. Vastleggen dat er uitsluitend de deelnemerscode in gaat, en dat in de SOP en het datamanagementplan zetten.</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>novel database, DMP</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>GDPR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" s="14">
+      <c r="A41" s="26" t="n"/>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>Back-up, bewaartermijn en opslaggrens</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>SQL Server Express is begrensd op 10 GB, 1 GB geheugen en 1 processor. Nagaan of 144 deelnemers x drie meetmomenten x twee condities daarbinnen past, en de back-up en de bewaartermijn vastleggen.</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>novel database, DMP</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
+        <is>
+          <t>Middel</t>
+        </is>
+      </c>
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="inlineStr">
+        <is>
+          <t>Handleiding db light p. 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" s="14">
+      <c r="A42" s="26" t="n"/>
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Route van de meetbestanden uit de zes centra</t>
+        </is>
+      </c>
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>Novel studio bewaart lokaal in C:\Users\Public\Documents\Novel Studio\plidar_data. Vastleggen hoe die bestanden bij het studieteam raken en onder welke naam ze in de database gaan.</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>SOP 09b, zes centra</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr">
+        <is>
+          <t>Hangt aan de formulierenroute</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" s="14">
+      <c r="A43" s="26" t="n"/>
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Frames uitsluiten — beantwoord</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>Data uitsluiten kan: 'file master' verwijdert de frames tussen twee markers. Een deelnemer die halverwege blijft staan kan dus uit de opname geknipt worden. Voor de norm blijft het overbodig, want MPP verandert niet door een pauze.</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>novel database</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t>Klaar</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr">
+        <is>
+          <t>Uitgezocht 11 sep</t>
         </is>
       </c>
     </row>
@@ -5357,7 +5554,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F29 F38:F43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Te doen,Bezig,Klaar,Geblokkeerd,Vervalt"</formula1>
     </dataValidation>
   </dataValidations>
